--- a/results/job_matches_2026-08-09.xlsx
+++ b/results/job_matches_2026-08-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,77 +538,77 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer with GCP experience</t>
+          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Oak Street Health, part of CVS Health</t>
+          <t>LRx Healthcare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314e85ac4ab93092</t>
+          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engg with DQ Exp</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffacc870aec02e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a5d6e6433a2545</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,120 +618,120 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Spark, PySpark, Scala, Time Travel</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08219ee125d81229</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8aea74abef8a18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Generative AI Developer</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ffffef4925474d</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9e9fc3b54ac213</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Machine Learning Infrastructure (Tinder LLC, West Hollywood, California)</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tinder</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52cf979ba77c87c</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ab23bad51bea29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LRx Healthcare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
+          <t>https://www.indeed.com/viewjob?jk=4f36e6ad2b9d5eee</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,77 +766,77 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+          <t>https://www.indeed.com/viewjob?jk=68e1984536652a6b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92503de4f5935b97</t>
+          <t>https://www.indeed.com/viewjob?jk=809d3d8f0cd3ba7c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irvington, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,102 +846,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8c2482782a25de3</t>
+          <t>https://www.indeed.com/viewjob?jk=7532420c47ab9918</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineering LMTS</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fff7b16fc0e3028</t>
+          <t>https://www.indeed.com/viewjob?jk=dddf5cf15398a1b2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
+          <t>https://www.indeed.com/viewjob?jk=9756f61fe64054a3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=e8825302d513b860</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineering MTS</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Spark, Scala, Kafka, NoSQL, Tableau, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1d5b5928313a4a3</t>
+          <t>https://www.indeed.com/viewjob?jk=78d05baf5131d057</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4f3d7b185f5214</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Devstringx Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1ccc7a2e90429f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,84 +1091,84 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=59825df715743788</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14f52354092168da</t>
+          <t>https://www.indeed.com/viewjob?jk=4262493a726203bf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+          <t>https://www.indeed.com/viewjob?jk=aa1471d4b9e4ee59</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,32 +1178,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e13ec741bfd9dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a493a3a015b49b5e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Palantir Foundry Data Engineer</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,85 +1213,85 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1f64b06c3394e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=4d594cd368db0cc1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Healthcare Imaging Solution Architect</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
+          <t>https://www.indeed.com/viewjob?jk=609f3d440406befd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Chicago Financial Search</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,40 +1301,1195 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
+          <t>https://www.indeed.com/viewjob?jk=cd31ed483ed0704a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=598255d64c547015</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf8834da6e7f65ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2ff83e97dc7a8e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d8eb0e239008fb91</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c0641e7484eeef7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b1a1f7304b51ad5</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3edd1688e6338ef5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a34666f446056f82</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fd8f9505867bd22</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5549813ef255d48e</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3c2bfd8979791eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba8387fe7fec0491</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d4442252fc45308</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a20858b0a8cf7284</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=823a2f7525ee8a91</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad3ff3f5a7f718e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57cba729b39e3c61</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2b740bac440ebbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49a7d66dee653b8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6353cece1e0232e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6db72a919d09ed4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6465cd205cfd827e</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2afcd1af85717687</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Google AI Architect</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d70bcefc31856e94</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Database Engineer II</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Chewy</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Plantation, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Data Architect – Snowflake</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>KT2i Inc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>DEPARTMENT OF BUILDINGS</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Devstringx Technologies</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Data Scientist Specialist - Customer Service</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Textron Aviation</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Healthcare Imaging Solution Architect</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>VeeRteq Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Software Development Engineer in Test</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Chicago Financial Search</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>San Antonio, TX, US USA</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="D59" t="n">
         <v>10.4</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1b9d27014bac5bbd</t>
         </is>

--- a/results/job_matches_2026-08-09.xlsx
+++ b/results/job_matches_2026-08-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2148,52 +2148,52 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af79dac6e5a615f</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Data Architect – Snowflake</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Devstringx Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Devstringx Technologies</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
+          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Chicago Financial Search</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Scientist Specialist - Customer Service</t>
+          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Textron Aviation</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Dask, Polars, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2385,111 +2385,6 @@
         </is>
       </c>
       <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=56f0af585b8a5603</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Healthcare Imaging Solution Architect</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>VeeRteq Solutions Inc.</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f78d5eab13424d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Chicago Financial Search</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>UT Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1b9d27014bac5bbd</t>
         </is>

--- a/results/job_matches_2026-08-09.xlsx
+++ b/results/job_matches_2026-08-09.xlsx
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
+          <t>Software Engineer II: Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LRx Healthcare</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ff2428319ab1fc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Google AI Architect</t>
+          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>LRx Healthcare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a5d6e6433a2545</t>
+          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8aea74abef8a18</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a5d6e6433a2545</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9e9fc3b54ac213</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8aea74abef8a18</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ab23bad51bea29</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9e9fc3b54ac213</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f36e6ad2b9d5eee</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ab23bad51bea29</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e1984536652a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=4f36e6ad2b9d5eee</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809d3d8f0cd3ba7c</t>
+          <t>https://www.indeed.com/viewjob?jk=68e1984536652a6b</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7532420c47ab9918</t>
+          <t>https://www.indeed.com/viewjob?jk=809d3d8f0cd3ba7c</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddf5cf15398a1b2</t>
+          <t>https://www.indeed.com/viewjob?jk=7532420c47ab9918</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9756f61fe64054a3</t>
+          <t>https://www.indeed.com/viewjob?jk=dddf5cf15398a1b2</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8825302d513b860</t>
+          <t>https://www.indeed.com/viewjob?jk=9756f61fe64054a3</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d05baf5131d057</t>
+          <t>https://www.indeed.com/viewjob?jk=e8825302d513b860</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4f3d7b185f5214</t>
+          <t>https://www.indeed.com/viewjob?jk=78d05baf5131d057</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1ccc7a2e90429f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4f3d7b185f5214</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59825df715743788</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1ccc7a2e90429f</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4262493a726203bf</t>
+          <t>https://www.indeed.com/viewjob?jk=59825df715743788</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa1471d4b9e4ee59</t>
+          <t>https://www.indeed.com/viewjob?jk=4262493a726203bf</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a493a3a015b49b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=aa1471d4b9e4ee59</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d594cd368db0cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=a493a3a015b49b5e</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609f3d440406befd</t>
+          <t>https://www.indeed.com/viewjob?jk=4d594cd368db0cc1</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd31ed483ed0704a</t>
+          <t>https://www.indeed.com/viewjob?jk=609f3d440406befd</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598255d64c547015</t>
+          <t>https://www.indeed.com/viewjob?jk=cd31ed483ed0704a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf8834da6e7f65ec</t>
+          <t>https://www.indeed.com/viewjob?jk=598255d64c547015</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ff83e97dc7a8e8</t>
+          <t>https://www.indeed.com/viewjob?jk=bf8834da6e7f65ec</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8eb0e239008fb91</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ff83e97dc7a8e8</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c0641e7484eeef7</t>
+          <t>https://www.indeed.com/viewjob?jk=d8eb0e239008fb91</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1a1f7304b51ad5</t>
+          <t>https://www.indeed.com/viewjob?jk=0c0641e7484eeef7</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3edd1688e6338ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1a1f7304b51ad5</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a34666f446056f82</t>
+          <t>https://www.indeed.com/viewjob?jk=3edd1688e6338ef5</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fd8f9505867bd22</t>
+          <t>https://www.indeed.com/viewjob?jk=a34666f446056f82</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5549813ef255d48e</t>
+          <t>https://www.indeed.com/viewjob?jk=5fd8f9505867bd22</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c2bfd8979791eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5549813ef255d48e</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba8387fe7fec0491</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c2bfd8979791eb</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4442252fc45308</t>
+          <t>https://www.indeed.com/viewjob?jk=ba8387fe7fec0491</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a20858b0a8cf7284</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4442252fc45308</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823a2f7525ee8a91</t>
+          <t>https://www.indeed.com/viewjob?jk=a20858b0a8cf7284</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3ff3f5a7f718e5</t>
+          <t>https://www.indeed.com/viewjob?jk=823a2f7525ee8a91</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57cba729b39e3c61</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3ff3f5a7f718e5</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b740bac440ebbb</t>
+          <t>https://www.indeed.com/viewjob?jk=57cba729b39e3c61</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a7d66dee653b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b740bac440ebbb</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6353cece1e0232e4</t>
+          <t>https://www.indeed.com/viewjob?jk=49a7d66dee653b8f</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6db72a919d09ed4</t>
+          <t>https://www.indeed.com/viewjob?jk=6353cece1e0232e4</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6465cd205cfd827e</t>
+          <t>https://www.indeed.com/viewjob?jk=b6db72a919d09ed4</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2afcd1af85717687</t>
+          <t>https://www.indeed.com/viewjob?jk=6465cd205cfd827e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,59 +2141,59 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70bcefc31856e94</t>
+          <t>https://www.indeed.com/viewjob?jk=2afcd1af85717687</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
+          <t>https://www.indeed.com/viewjob?jk=d70bcefc31856e94</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake</t>
+          <t>Database Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Architect – Snowflake</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Devstringx Technologies</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Devstringx Technologies</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b44530688ac699b</t>
+          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-09.xlsx
+++ b/results/job_matches_2026-08-09.xlsx
@@ -2218,17 +2218,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Architect – Snowflake</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-09.xlsx
+++ b/results/job_matches_2026-08-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Database Engineer II</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Snowflake, Oracle, ETL, ELT, dbt, CI/CD, Terraform</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fd6049b5c3fb13e</t>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Architect – Snowflake</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>Devstringx Technologies</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Devstringx Technologies</t>
+          <t>Chicago Financial Search</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test</t>
+          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chicago Financial Search</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,50 +2341,15 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
+          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>UT Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1b9d27014bac5bbd</t>
         </is>

--- a/results/job_matches_2026-08-09.xlsx
+++ b/results/job_matches_2026-08-09.xlsx
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Architect – Snowflake</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-09.xlsx
+++ b/results/job_matches_2026-08-09.xlsx
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>DEPARTMENT OF BUILDINGS</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Architect – Snowflake</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-09.xlsx
+++ b/results/job_matches_2026-08-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Developer / Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Glue, EMR, Kinesis, S3, SQS, IAM, RDS, HBase, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c2beecd9e43cf9c</t>
+          <t>https://www.indeed.com/viewjob?jk=3f4670b855a27725</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Java Developer / Architect</t>
+          <t>Software Engineer II: Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f4670b855a27725</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ff2428319ab1fc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II: Data Engineer</t>
+          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>LRx Healthcare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ff2428319ab1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LRx Healthcare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a5d6e6433a2545</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a5d6e6433a2545</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8aea74abef8a18</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8aea74abef8a18</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9e9fc3b54ac213</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9e9fc3b54ac213</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ab23bad51bea29</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ab23bad51bea29</t>
+          <t>https://www.indeed.com/viewjob?jk=4f36e6ad2b9d5eee</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f36e6ad2b9d5eee</t>
+          <t>https://www.indeed.com/viewjob?jk=68e1984536652a6b</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e1984536652a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=809d3d8f0cd3ba7c</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809d3d8f0cd3ba7c</t>
+          <t>https://www.indeed.com/viewjob?jk=7532420c47ab9918</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7532420c47ab9918</t>
+          <t>https://www.indeed.com/viewjob?jk=dddf5cf15398a1b2</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddf5cf15398a1b2</t>
+          <t>https://www.indeed.com/viewjob?jk=9756f61fe64054a3</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9756f61fe64054a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e8825302d513b860</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8825302d513b860</t>
+          <t>https://www.indeed.com/viewjob?jk=78d05baf5131d057</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d05baf5131d057</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4f3d7b185f5214</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4f3d7b185f5214</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1ccc7a2e90429f</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1ccc7a2e90429f</t>
+          <t>https://www.indeed.com/viewjob?jk=59825df715743788</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59825df715743788</t>
+          <t>https://www.indeed.com/viewjob?jk=4262493a726203bf</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4262493a726203bf</t>
+          <t>https://www.indeed.com/viewjob?jk=aa1471d4b9e4ee59</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa1471d4b9e4ee59</t>
+          <t>https://www.indeed.com/viewjob?jk=a493a3a015b49b5e</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a493a3a015b49b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d594cd368db0cc1</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d594cd368db0cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=609f3d440406befd</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609f3d440406befd</t>
+          <t>https://www.indeed.com/viewjob?jk=cd31ed483ed0704a</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd31ed483ed0704a</t>
+          <t>https://www.indeed.com/viewjob?jk=598255d64c547015</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598255d64c547015</t>
+          <t>https://www.indeed.com/viewjob?jk=bf8834da6e7f65ec</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf8834da6e7f65ec</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ff83e97dc7a8e8</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ff83e97dc7a8e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d8eb0e239008fb91</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8eb0e239008fb91</t>
+          <t>https://www.indeed.com/viewjob?jk=0c0641e7484eeef7</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c0641e7484eeef7</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1a1f7304b51ad5</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1a1f7304b51ad5</t>
+          <t>https://www.indeed.com/viewjob?jk=3edd1688e6338ef5</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3edd1688e6338ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=a34666f446056f82</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a34666f446056f82</t>
+          <t>https://www.indeed.com/viewjob?jk=5fd8f9505867bd22</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fd8f9505867bd22</t>
+          <t>https://www.indeed.com/viewjob?jk=5549813ef255d48e</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5549813ef255d48e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c2bfd8979791eb</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c2bfd8979791eb</t>
+          <t>https://www.indeed.com/viewjob?jk=ba8387fe7fec0491</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba8387fe7fec0491</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4442252fc45308</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4442252fc45308</t>
+          <t>https://www.indeed.com/viewjob?jk=a20858b0a8cf7284</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a20858b0a8cf7284</t>
+          <t>https://www.indeed.com/viewjob?jk=823a2f7525ee8a91</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823a2f7525ee8a91</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3ff3f5a7f718e5</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3ff3f5a7f718e5</t>
+          <t>https://www.indeed.com/viewjob?jk=57cba729b39e3c61</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57cba729b39e3c61</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b740bac440ebbb</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b740bac440ebbb</t>
+          <t>https://www.indeed.com/viewjob?jk=49a7d66dee653b8f</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a7d66dee653b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=6353cece1e0232e4</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6353cece1e0232e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b6db72a919d09ed4</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6db72a919d09ed4</t>
+          <t>https://www.indeed.com/viewjob?jk=6465cd205cfd827e</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6465cd205cfd827e</t>
+          <t>https://www.indeed.com/viewjob?jk=2afcd1af85717687</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2afcd1af85717687</t>
+          <t>https://www.indeed.com/viewjob?jk=d70bcefc31856e94</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Google AI Architect</t>
+          <t>Data Architect – Snowflake</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>KT2i Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70bcefc31856e94</t>
+          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DEPARTMENT OF BUILDINGS</t>
+          <t>Devstringx Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71d49715069e7479</t>
+          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake</t>
+          <t>Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>Chicago Financial Search</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,110 +2246,40 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Devstringx Technologies</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Chicago Financial Search</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>UT Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1b9d27014bac5bbd</t>
         </is>

--- a/results/job_matches_2026-08-09.xlsx
+++ b/results/job_matches_2026-08-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect – Snowflake</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>KT2i Inc</t>
+          <t>Devstringx Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78d1b05e07aa732</t>
+          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Devstringx Technologies</t>
+          <t>Chicago Financial Search</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
+          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test</t>
+          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chicago Financial Search</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,50 +2236,15 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
+          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>UT Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1b9d27014bac5bbd</t>
         </is>

--- a/results/job_matches_2026-08-09.xlsx
+++ b/results/job_matches_2026-08-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Java Developer / Architect</t>
+          <t>Software Engineer II: Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f4670b855a27725</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ff2428319ab1fc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II: Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>VBEST Software Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, S3, IAM, Databricks, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ff2428319ab1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=539879c923ff55f6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer – Sales Incentive Compensation (SIC)</t>
+          <t>Google AI Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LRx Healthcare</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7cc2ef3ea91ac6c</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a5d6e6433a2545</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a5d6e6433a2545</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8aea74abef8a18</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8aea74abef8a18</t>
+          <t>https://www.indeed.com/viewjob?jk=ea9e9fc3b54ac213</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea9e9fc3b54ac213</t>
+          <t>https://www.indeed.com/viewjob?jk=f2ab23bad51bea29</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2ab23bad51bea29</t>
+          <t>https://www.indeed.com/viewjob?jk=4f36e6ad2b9d5eee</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f36e6ad2b9d5eee</t>
+          <t>https://www.indeed.com/viewjob?jk=68e1984536652a6b</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68e1984536652a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=809d3d8f0cd3ba7c</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=809d3d8f0cd3ba7c</t>
+          <t>https://www.indeed.com/viewjob?jk=7532420c47ab9918</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7532420c47ab9918</t>
+          <t>https://www.indeed.com/viewjob?jk=dddf5cf15398a1b2</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dddf5cf15398a1b2</t>
+          <t>https://www.indeed.com/viewjob?jk=9756f61fe64054a3</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9756f61fe64054a3</t>
+          <t>https://www.indeed.com/viewjob?jk=e8825302d513b860</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8825302d513b860</t>
+          <t>https://www.indeed.com/viewjob?jk=78d05baf5131d057</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78d05baf5131d057</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4f3d7b185f5214</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4f3d7b185f5214</t>
+          <t>https://www.indeed.com/viewjob?jk=3f1ccc7a2e90429f</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f1ccc7a2e90429f</t>
+          <t>https://www.indeed.com/viewjob?jk=59825df715743788</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59825df715743788</t>
+          <t>https://www.indeed.com/viewjob?jk=4262493a726203bf</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4262493a726203bf</t>
+          <t>https://www.indeed.com/viewjob?jk=aa1471d4b9e4ee59</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa1471d4b9e4ee59</t>
+          <t>https://www.indeed.com/viewjob?jk=a493a3a015b49b5e</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a493a3a015b49b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d594cd368db0cc1</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d594cd368db0cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=609f3d440406befd</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609f3d440406befd</t>
+          <t>https://www.indeed.com/viewjob?jk=cd31ed483ed0704a</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd31ed483ed0704a</t>
+          <t>https://www.indeed.com/viewjob?jk=598255d64c547015</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=598255d64c547015</t>
+          <t>https://www.indeed.com/viewjob?jk=bf8834da6e7f65ec</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf8834da6e7f65ec</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ff83e97dc7a8e8</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ff83e97dc7a8e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d8eb0e239008fb91</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8eb0e239008fb91</t>
+          <t>https://www.indeed.com/viewjob?jk=0c0641e7484eeef7</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c0641e7484eeef7</t>
+          <t>https://www.indeed.com/viewjob?jk=1b1a1f7304b51ad5</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b1a1f7304b51ad5</t>
+          <t>https://www.indeed.com/viewjob?jk=3edd1688e6338ef5</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3edd1688e6338ef5</t>
+          <t>https://www.indeed.com/viewjob?jk=a34666f446056f82</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a34666f446056f82</t>
+          <t>https://www.indeed.com/viewjob?jk=5fd8f9505867bd22</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fd8f9505867bd22</t>
+          <t>https://www.indeed.com/viewjob?jk=5549813ef255d48e</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5549813ef255d48e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c2bfd8979791eb</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c2bfd8979791eb</t>
+          <t>https://www.indeed.com/viewjob?jk=ba8387fe7fec0491</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba8387fe7fec0491</t>
+          <t>https://www.indeed.com/viewjob?jk=1d4442252fc45308</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d4442252fc45308</t>
+          <t>https://www.indeed.com/viewjob?jk=a20858b0a8cf7284</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a20858b0a8cf7284</t>
+          <t>https://www.indeed.com/viewjob?jk=823a2f7525ee8a91</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823a2f7525ee8a91</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3ff3f5a7f718e5</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3ff3f5a7f718e5</t>
+          <t>https://www.indeed.com/viewjob?jk=57cba729b39e3c61</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57cba729b39e3c61</t>
+          <t>https://www.indeed.com/viewjob?jk=c2b740bac440ebbb</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2b740bac440ebbb</t>
+          <t>https://www.indeed.com/viewjob?jk=49a7d66dee653b8f</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49a7d66dee653b8f</t>
+          <t>https://www.indeed.com/viewjob?jk=6353cece1e0232e4</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6353cece1e0232e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b6db72a919d09ed4</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6db72a919d09ed4</t>
+          <t>https://www.indeed.com/viewjob?jk=6465cd205cfd827e</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6465cd205cfd827e</t>
+          <t>https://www.indeed.com/viewjob?jk=2afcd1af85717687</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2afcd1af85717687</t>
+          <t>https://www.indeed.com/viewjob?jk=d70bcefc31856e94</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Google AI Architect</t>
+          <t>Software Development Engineer in Test</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Chicago Financial Search</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, Jenkins</t>
+          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,110 +2141,40 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d70bcefc31856e94</t>
+          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Devstringx Technologies</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1832c0accdf9751b</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Software Development Engineer in Test</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Chicago Financial Search</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>UT Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1b9d27014bac5bbd</t>
         </is>

--- a/results/job_matches_2026-08-09.xlsx
+++ b/results/job_matches_2026-08-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test</t>
+          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chicago Financial Search</t>
+          <t>UT Health Science Center at San Antonio</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,50 +2131,15 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Scala, Kafka, ELT, MLflow, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest, Git</t>
+          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f469ade2831899c</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>UT Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1b9d27014bac5bbd</t>
         </is>

--- a/results/job_matches_2026-08-09.xlsx
+++ b/results/job_matches_2026-08-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2110,41 +2110,6 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Clinical Business Intelligence Analyst (EPIC)-Sr</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>UT Health Science Center at San Antonio</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Data Modeling, ETL, ELT, Power BI, Tableau, Git, Python</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b9d27014bac5bbd</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
